--- a/data/Tablas/Base_Datos_Integrada_Sinergia_Chachajo.xlsx
+++ b/data/Tablas/Base_Datos_Integrada_Sinergia_Chachajo.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen General" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Puntos Estratégicos &amp; GIS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hidrografía &amp; Restauración" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biodiversidad &amp; Etnobiología" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseño Cámaras Trampa" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gobernanza &amp; Organización" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Resumen General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Puntos Estratégicos &amp; GIS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Hidrografía &amp; Restauración" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Biodiversidad &amp; Etnobiología" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Diseño Cámaras Trampa" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gobernanza &amp; Organización" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Fauna local" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Flora local" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +62,9 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -87,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,11 +114,17 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +170,9 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1584,7 +1598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -1922,8 +1935,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
@@ -2866,4 +2877,712 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FAUNA LOCAL (ANIMALES)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nombre Común</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nombre en Lengua (Woun)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Categoría / Hábitat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Interacciones Ecológicas / Alimentación (Lámina 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Guagua</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ëur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mamífero Terrestre / Bosque denso</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Se alimenta de la palma de Milpesos / Sérbago (Lámina 2 de interacciones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tucán</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>khea-pan / Tucan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ave / Dosel del bosque</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Se alimenta de frutos de Popo por caldo de popo y Wegwer beu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Loro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lorit / Loro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ave / Dosel del bosque</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Interactúa fuertemente y se alimenta de la fruta de Popo por caldo de popo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guatín</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>echkhum / Guatin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mamífero Terrestre / Sotobosque</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Se alimenta de los frutos caídos de la palma de Toparo (Thophor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ardilla</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ardit / Ardilla</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mamífero Pequeño / Arbóreo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Consume frutos de la palma Wegwer beu y Toparo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Venado</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mamífero Mediano / Bosque interior</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Registrado en el inventario de censo y monitoreado por cámaras trampa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tatabro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mamífero / Suelo forestal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Especie cinegética clave para la seguridad alimentaria de la comunidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saino</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mamífero / Suelo forestal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Puerco de monte, de alto valor proteico y cultural</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cusumbo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mamífero / Arbóreo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Especie dispersora de semillas en el dosel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tigre (Jaguar/Puma)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felino Grande / Depredador tope</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Indicador biológico definitivo de la excelente salud del bosque</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cachama</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pez de Río / Acuático</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Especie fundamental de la pesca artesanal en el Río San Juan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tortuga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Reptil / Anfibio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Habita las riberas del Río San Juan y las quebradas tranquilas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Armadillo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mamífero / Excavador</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Habita en el suelo del bosque ribereño, se alimenta de insectos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Babilla</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Reptil / Ribereño</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Habita en las zonas bajas e inundables del río</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FLORA LOCAL (PLANTAS)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nombre de la Planta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nombre Alternativo / Lengua</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Uso Tradicional / Importancia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Presencia en Cartografía Social</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Milpesos / Sérbago</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Palma de Milpesos</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alimenticio (fruta y aceite) y artesanal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Palma clave dibujada en la red trófica (Lámina 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Popo por caldo de popo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Popo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alimenticio y medicinal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Árbol frutal destacado del bosque nativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Toparo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thophor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Especie forestal nativa proveedora de semillas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dibujada como soporte alimentario del Guatín y la Ardilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wegwer beu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Palma Wegwerbeu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Uso estructural y alimentario de fauna</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Especie forestal del bosque maduro ribereño</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chachajo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Árbol de Chachajo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Madera preciosa y de alto valor espiritual</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Da nombre al resguardo y a las quebradas; especie emblemática</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guayacán</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Árbol maderable</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Construcción tradicional de palafitos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mapeado en la zona de 'Bocon Reforestal'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Matarratón &amp; Nacedero</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Plantas protectoras</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Protección de nacimientos de agua y cercas vivas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Asociadas al cuidado de las microcuencas de las quebradas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Naidí / Asaí</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Palma de Naidí</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Alimenticio (súperfruta) y económico</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Palma silvestre de zonas inundables muy valorada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Borojó &amp; Zapote</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Frutales amazónicos/pacíficos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Alimenticio y medicinal familiar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sembrados en los huertos contiguos a las viviendas tradicionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hoja de Culebra / Hoja de Caimán</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plantas medicinales</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Medicina ancestral de parteras y conocedores</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mencionadas explícitamente en el inventario del Comité de Planta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Papachina</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tubérculo tradicional</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Soberanía alimentaria (cultivo de pancoger)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Dibujado en zonas agrícolas de la margen del río (Lámina 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jagua &amp; Achote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Plantas tintóreas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pintura corporal tradicional y artesanías</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Especies cultivadas cerca de la Casa Grande y el Colegio</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Tablas/Base_Datos_Integrada_Sinergia_Chachajo.xlsx
+++ b/data/Tablas/Base_Datos_Integrada_Sinergia_Chachajo.xlsx
@@ -539,132 +539,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PROYECTO SINERGIA: CARTOGRAFÍA ECO-CULTURAL WOUNAAN</t>
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Métrica de Proyecto</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Valor / Detalle Integrado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Integración de Datos Técnicos SIG e Información Ancestral (Resguardo Chachajo, Buenaventura)</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Comunidad Principal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chachajo (Pueblo Woun / Wounaan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ubicación Regional</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Buenaventura, Valle del Cauca, Chocó Biogeográfico, Colombia</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Métrica de Proyecto</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Valor / Detalle Integrado</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Puntos Técnicos Registrados</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Comunidad Principal</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Chachajo (Pueblo Woun / Wounaan)</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sitios de Alto Valor / Estratégicos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Ubicación Regional</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Buenaventura, Valle del Cauca, Chocó Biogeográfico, Colombia</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Especies de Fauna Registradas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Río Eje</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Río San Juan</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Especies de Flora Registradas</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Puntos Técnicos Registrados</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Sitios de Alto Valor / Estratégicos</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Cámaras Trampa Diseñadas</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Especies de Fauna Registradas</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Especies de Flora Registradas</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Polígono de Restauración Activa</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>21.35 Hectáreas (Quebrada Chachajo)</t>
         </is>
@@ -1281,284 +1249,268 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="71" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="196" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cuerpos de Agua y Polígonos de Restauración Ambiental</t>
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Nombre del Cuerpo de Agua / Microtopónimo</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Tipo / Uso Técnico</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Área Conservación (Ha)</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Descripción en Cartografía Social Wounaan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Río Eje y Quebradas registradas por la comunidad y validadas por SIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Nombre del Cuerpo de Agua / Microtopónimo</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Tipo / Uso Técnico</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Área Conservación (Ha)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Descripción en Cartografía Social Wounaan</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Río San Juan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Río Eje Principal / Transporte y Pesca Artesanal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Eje central de la vida comunitaria, divide el territorio en dos franjas habitacionales y productivas. Dibujado en todas las láminas con fauna acuática (Cachama, Saltón, Tortuga, Pato, Biringo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Quebrada Chachajo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quebrada / Polígono de Restauración Activa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>21.34</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sitio Sagrado y área prioritaria para restauración eco-cultural. Asociada a la reforestación comunitaria de especies maderables y espirituales.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Río San Juan</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Río Eje Principal / Transporte y Pesca Artesanal</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Eje central de la vida comunitaria, divide el territorio en dos franjas habitacionales y productivas. Dibujado en todas las láminas con fauna acuática (Cachama, Saltón, Tortuga, Pato, Biringo).</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Quebrada Papayo / Q. Pepepan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quebrada Tributaria</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Por delimitar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Identificada en los mapas comunitarios como zona de recolección de plantas medicinales y protección de microcuencas.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada Chachajo</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada / Polígono de Restauración Activa</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>21.34</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Sitio Sagrado y área prioritaria para restauración eco-cultural. Asociada a la reforestación comunitaria de especies maderables y espirituales.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Quebrada Chachajito</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quebrada Tributaria</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Por delimitar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ubicada contigua al poblado, zona de viviendas y huertas tradicionales familiares.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Quebrada Papayo / Q. Pepepan</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Quebrada Cocowe</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Identificada en los mapas comunitarios como zona de recolección de plantas medicinales y protección de microcuencas.</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Identificada en el mapa central del territorio por el Grupo 2.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada Chachajito</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Quebrada Cielito</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Ubicada contigua al poblado, zona de viviendas y huertas tradicionales familiares.</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cuerpo de agua tributario de la margen izquierda del Río San Juan.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Quebrada Cocowe</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Quebrada Cupenpito</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Identificada en el mapa central del territorio por el Grupo 2.</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Drenaje verificado en los talleres de cartografía social comunitaria.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada Cielito</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Quebrada Limoncito</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Cuerpo de agua tributario de la margen izquierda del Río San Juan.</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ubicada en la margen derecha, zona boscosa para avonamiento y tránsito de fauna.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Quebrada Cupenpito</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Quebrada Liguorio</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Drenaje verificado en los talleres de cartografía social comunitaria.</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Drenaje menor de alta importancia para el abastecimiento y monitoreo.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada Limoncito</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Quebrada Valencia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Ubicada en la margen derecha, zona boscosa para avonamiento y tránsito de fauna.</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quebrada en la zona sur, cercana al área habitada e infraestructura escolar.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Quebrada Liguorio</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Quebrada Laureano</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Quebrada Tributaria</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Por delimitar</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Drenaje menor de alta importancia para el abastecimiento y monitoreo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada Valencia</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada Tributaria</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Por delimitar</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Quebrada en la zona sur, cercana al área habitada e infraestructura escolar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Quebrada Laureano</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Quebrada Tributaria</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Por delimitar</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Límite exterior mapeado por el Grupo 3 en los talleres eco-culturales.</t>
         </is>
@@ -2916,9 +2868,6 @@
           <t>FAUNA LOCAL (ANIMALES)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3256,9 +3205,6 @@
           <t>FLORA LOCAL (PLANTAS)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
